--- a/import.xlsx
+++ b/import.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="120" windowWidth="11550" windowHeight="8000" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="8940" yWindow="120" windowWidth="11550" windowHeight="8000" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Растворители" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="92">
   <si>
     <t>Шифр</t>
   </si>
@@ -255,6 +255,48 @@
   </si>
   <si>
     <t>Показатели остр. токсичности</t>
+  </si>
+  <si>
+    <t>Руб</t>
+  </si>
+  <si>
+    <t>Шифр1</t>
+  </si>
+  <si>
+    <t>Название1</t>
+  </si>
+  <si>
+    <t>Шифр2</t>
+  </si>
+  <si>
+    <t>Название2</t>
+  </si>
+  <si>
+    <t>Шифр3</t>
+  </si>
+  <si>
+    <t>Название3</t>
+  </si>
+  <si>
+    <t>Шифр4</t>
+  </si>
+  <si>
+    <t>Название4</t>
+  </si>
+  <si>
+    <t>Шифр5</t>
+  </si>
+  <si>
+    <t>Название5</t>
+  </si>
+  <si>
+    <t>Шифр6</t>
+  </si>
+  <si>
+    <t>Название6</t>
+  </si>
+  <si>
+    <t>Платность растворителя</t>
   </si>
 </sst>
 </file>
@@ -912,9 +954,106 @@
       <c r="B3" s="3"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3"/>
-      <c r="G4" s="5"/>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20">
+        <v>1</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="20">
+        <v>2</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="20">
+        <v>3</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC4" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG4" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
@@ -2813,7 +2952,7 @@
     <col min="31" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -2926,13 +3065,118 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="D2" s="4"/>
-      <c r="G2" s="5"/>
-      <c r="I2" s="4"/>
-      <c r="U2" s="4"/>
+    <row r="2" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="20">
+        <v>1</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="20">
+        <v>2</v>
+      </c>
+      <c r="L2" s="20">
+        <v>3</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="20">
+        <v>4</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK2" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
@@ -4805,7 +5049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AO29"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" style="15" bestFit="1" customWidth="1"/>
@@ -4837,7 +5081,7 @@
     <col min="28" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -4890,160 +5134,282 @@
         <v>60</v>
       </c>
       <c r="R1" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="S1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="Y1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AK1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AK1" s="11" t="s">
+      <c r="AL1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="11" t="s">
+      <c r="AM1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AM1" s="11" t="s">
+      <c r="AN1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AO1" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="20">
+        <v>2</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="20">
+        <v>3</v>
+      </c>
+      <c r="L2" s="20">
+        <v>4</v>
+      </c>
+      <c r="M2" s="20">
+        <v>5</v>
+      </c>
+      <c r="N2" s="20">
+        <v>6</v>
+      </c>
+      <c r="O2" s="20">
+        <v>7</v>
+      </c>
+      <c r="P2" s="20">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="20">
+        <v>9</v>
+      </c>
+      <c r="R2" s="20">
+        <v>11</v>
+      </c>
+      <c r="S2" s="20">
+        <v>10</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO2" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="3"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="3"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
@@ -5263,11 +5629,109 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="G2" s="5"/>
-      <c r="R2" s="4"/>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="20">
+        <v>2</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="20">
+        <v>3</v>
+      </c>
+      <c r="L2" s="20">
+        <v>4</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
@@ -6194,7 +6658,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT350"/>
+  <dimension ref="A1:AU350"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.1796875" style="15" bestFit="1" customWidth="1"/>
@@ -6245,7 +6709,7 @@
     <col min="47" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -6282,208 +6746,347 @@
       <c r="L1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="O1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="15" t="s">
+      <c r="AA1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="15" t="s">
+      <c r="AC1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="15" t="s">
+      <c r="AD1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="15" t="s">
+      <c r="AE1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AK1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="AK1" s="11" t="s">
+      <c r="AL1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AL1" s="11" t="s">
+      <c r="AM1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AM1" s="11" t="s">
+      <c r="AN1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AO1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AP1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AP1" s="11" t="s">
+      <c r="AQ1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AQ1" s="11" t="s">
+      <c r="AR1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="AS1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AT1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AT1" s="11" t="s">
+      <c r="AU1" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="F2" s="5"/>
-      <c r="N2" s="12"/>
-      <c r="AD2" s="4"/>
-    </row>
-    <row r="3" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="20">
+        <v>2</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="20">
+        <v>3</v>
+      </c>
+      <c r="K2" s="20">
+        <v>4</v>
+      </c>
+      <c r="L2" s="20">
+        <v>5</v>
+      </c>
+      <c r="M2" s="20">
+        <v>7</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" s="20">
+        <v>6</v>
+      </c>
+      <c r="AA2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU2" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="F3" s="5"/>
       <c r="N3" s="12"/>
       <c r="AD3" s="4"/>
     </row>
-    <row r="4" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="F4" s="5"/>
       <c r="N4" s="12"/>
       <c r="AD4" s="4"/>
     </row>
-    <row r="5" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="F5" s="5"/>
       <c r="N5" s="12"/>
       <c r="AD5" s="4"/>
     </row>
-    <row r="6" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="F6" s="14"/>
       <c r="N6" s="12"/>
       <c r="AD6" s="4"/>
     </row>
-    <row r="7" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="F7" s="5"/>
       <c r="N7" s="12"/>
       <c r="AD7" s="4"/>
     </row>
-    <row r="8" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="F8" s="5"/>
       <c r="N8" s="12"/>
       <c r="AD8" s="4"/>
     </row>
-    <row r="9" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="F9" s="5"/>
       <c r="N9" s="12"/>
       <c r="AD9" s="4"/>
     </row>
-    <row r="10" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="3"/>
       <c r="F10" s="5"/>
       <c r="N10" s="12"/>
       <c r="AD10" s="4"/>
     </row>
-    <row r="11" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="F11" s="5"/>
       <c r="N11" s="12"/>
       <c r="AD11" s="4"/>
     </row>
-    <row r="12" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="3"/>
       <c r="F12" s="5"/>
       <c r="N12" s="12"/>
       <c r="AD12" s="4"/>
     </row>
-    <row r="13" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="F13" s="5"/>
       <c r="N13" s="12"/>
       <c r="AD13" s="4"/>
     </row>
-    <row r="14" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="F14" s="5"/>
       <c r="N14" s="12"/>
       <c r="AD14" s="4"/>
     </row>
-    <row r="15" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="F15" s="5"/>
       <c r="N15" s="12"/>
       <c r="AD15" s="4"/>
     </row>
-    <row r="16" spans="1:46" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="F16" s="5"/>
@@ -7791,7 +8394,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG274"/>
+  <dimension ref="A1:AH274"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.7265625" style="15" bestFit="1" customWidth="1"/>
@@ -7805,7 +8408,7 @@
     <col min="9" max="9" width="15.26953125" style="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.453125" style="15" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.1796875" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.08984375" style="15" customWidth="1"/>
     <col min="13" max="13" width="15.81640625" style="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.81640625" style="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.26953125" style="15" bestFit="1" customWidth="1"/>
@@ -7830,7 +8433,7 @@
     <col min="34" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -7862,160 +8465,261 @@
         <v>10</v>
       </c>
       <c r="K1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="O1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="X1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="11" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="F2" s="5"/>
-      <c r="Q2" s="4"/>
-    </row>
-    <row r="3" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="20">
+        <v>2</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="20">
+        <v>3</v>
+      </c>
+      <c r="K2" s="20">
+        <v>7</v>
+      </c>
+      <c r="L2" s="20">
+        <v>4</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
       <c r="F3" s="5"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="38"/>
       <c r="B4" s="38"/>
       <c r="F4" s="5"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="38"/>
       <c r="B5" s="38"/>
       <c r="F5" s="5"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="38"/>
       <c r="B6" s="38"/>
       <c r="F6" s="5"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="38"/>
       <c r="B7" s="38"/>
       <c r="F7" s="5"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="38"/>
       <c r="B8" s="38"/>
       <c r="F8" s="5"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="38"/>
       <c r="B9" s="38"/>
       <c r="F9" s="5"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="38"/>
       <c r="B10" s="38"/>
       <c r="F10" s="5"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38"/>
       <c r="B11" s="38"/>
       <c r="F11" s="5"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="38"/>
       <c r="B12" s="38"/>
       <c r="F12" s="5"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38"/>
       <c r="B13" s="38"/>
       <c r="F13" s="5"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="38"/>
       <c r="B14" s="38"/>
       <c r="F14" s="8"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38"/>
       <c r="B15" s="38"/>
       <c r="F15" s="5"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="38"/>
       <c r="B16" s="38"/>
       <c r="F16" s="5"/>
@@ -9021,7 +9725,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AO31"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" style="15" bestFit="1" customWidth="1"/>
@@ -9067,7 +9771,7 @@
     <col min="41" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -9108,98 +9812,216 @@
         <v>50</v>
       </c>
       <c r="N1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="U1" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="Y1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AK1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AK1" s="11" t="s">
+      <c r="AL1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="11" t="s">
+      <c r="AM1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AM1" s="11" t="s">
+      <c r="AN1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AO1" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="20">
+        <v>2</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="20">
+        <v>3</v>
+      </c>
+      <c r="L2" s="20">
+        <v>4</v>
+      </c>
+      <c r="M2" s="20">
+        <v>5</v>
+      </c>
+      <c r="N2" s="20">
+        <v>8</v>
+      </c>
+      <c r="O2" s="20">
+        <v>6</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="U2" s="20">
+        <v>7</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO2" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
       <c r="C3" s="11"/>
@@ -9209,7 +10031,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="38"/>
       <c r="B4" s="38"/>
       <c r="C4" s="11"/>
@@ -9219,7 +10041,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5" s="38"/>
       <c r="B5" s="38"/>
       <c r="C5" s="11"/>
@@ -9229,7 +10051,7 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" s="38"/>
       <c r="B6" s="38"/>
       <c r="C6" s="11"/>
@@ -9239,7 +10061,7 @@
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7" s="38"/>
       <c r="B7" s="38"/>
       <c r="C7" s="11"/>
@@ -9249,7 +10071,7 @@
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8" s="38"/>
       <c r="B8" s="38"/>
       <c r="C8" s="11"/>
@@ -9259,7 +10081,7 @@
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" s="38"/>
       <c r="B9" s="38"/>
       <c r="C9" s="11"/>
@@ -9269,7 +10091,7 @@
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" s="38"/>
       <c r="B10" s="38"/>
       <c r="C10" s="11"/>
@@ -9279,7 +10101,7 @@
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" s="38"/>
       <c r="B11" s="38"/>
       <c r="C11" s="11"/>
@@ -9289,7 +10111,7 @@
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" s="38"/>
       <c r="B12" s="38"/>
       <c r="C12" s="11"/>
@@ -9299,7 +10121,7 @@
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A13" s="38"/>
       <c r="B13" s="38"/>
       <c r="C13" s="11"/>
@@ -9309,7 +10131,7 @@
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A14" s="38"/>
       <c r="B14" s="38"/>
       <c r="C14" s="11"/>
@@ -9319,7 +10141,7 @@
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" s="38"/>
       <c r="B15" s="38"/>
       <c r="C15" s="11"/>
@@ -9329,7 +10151,7 @@
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" s="38"/>
       <c r="B16" s="38"/>
       <c r="C16" s="11"/>
@@ -9529,9 +10351,24 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>

--- a/import.xlsx
+++ b/import.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="120" windowWidth="11550" windowHeight="8000" firstSheet="3" activeTab="7"/>
+    <workbookView xWindow="8940" yWindow="120" windowWidth="11550" windowHeight="8000"/>
   </bookViews>
   <sheets>
     <sheet name="Растворители" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="79">
   <si>
     <t>Шифр</t>
   </si>
@@ -255,45 +255,6 @@
   </si>
   <si>
     <t>Показатели остр. токсичности</t>
-  </si>
-  <si>
-    <t>Руб</t>
-  </si>
-  <si>
-    <t>Шифр1</t>
-  </si>
-  <si>
-    <t>Название1</t>
-  </si>
-  <si>
-    <t>Шифр2</t>
-  </si>
-  <si>
-    <t>Название2</t>
-  </si>
-  <si>
-    <t>Шифр3</t>
-  </si>
-  <si>
-    <t>Название3</t>
-  </si>
-  <si>
-    <t>Шифр4</t>
-  </si>
-  <si>
-    <t>Название4</t>
-  </si>
-  <si>
-    <t>Шифр5</t>
-  </si>
-  <si>
-    <t>Название5</t>
-  </si>
-  <si>
-    <t>Шифр6</t>
-  </si>
-  <si>
-    <t>Название6</t>
   </si>
   <si>
     <t>Платность растворителя</t>
@@ -954,107 +915,7 @@
       <c r="B3" s="3"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="20">
-        <v>2</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="20">
-        <v>3</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="X4" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC4" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD4" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF4" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG4" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="4" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
       <c r="G5" s="5"/>
@@ -3065,119 +2926,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="20">
-        <v>1</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="20">
-        <v>2</v>
-      </c>
-      <c r="L2" s="20">
-        <v>3</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="20">
-        <v>4</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK2" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="2" spans="1:37" s="11" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
@@ -5134,7 +4883,7 @@
         <v>60</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="S1" s="20" t="s">
         <v>21</v>
@@ -5206,131 +4955,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="20">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="20">
-        <v>2</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="20">
-        <v>3</v>
-      </c>
-      <c r="L2" s="20">
-        <v>4</v>
-      </c>
-      <c r="M2" s="20">
-        <v>5</v>
-      </c>
-      <c r="N2" s="20">
-        <v>6</v>
-      </c>
-      <c r="O2" s="20">
-        <v>7</v>
-      </c>
-      <c r="P2" s="20">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="20">
-        <v>9</v>
-      </c>
-      <c r="R2" s="20">
-        <v>11</v>
-      </c>
-      <c r="S2" s="20">
-        <v>10</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AO2" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="2" spans="1:41" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
@@ -5629,110 +5254,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="20">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="20">
-        <v>2</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="20">
-        <v>3</v>
-      </c>
-      <c r="L2" s="20">
-        <v>4</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="2" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
@@ -6852,149 +6374,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="20">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="20">
-        <v>2</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="20">
-        <v>3</v>
-      </c>
-      <c r="K2" s="20">
-        <v>4</v>
-      </c>
-      <c r="L2" s="20">
-        <v>5</v>
-      </c>
-      <c r="M2" s="20">
-        <v>7</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z2" s="20">
-        <v>6</v>
-      </c>
-      <c r="AA2" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AP2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AR2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU2" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="2" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:47" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
@@ -8537,110 +7917,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="20">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="20">
-        <v>2</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="20">
-        <v>3</v>
-      </c>
-      <c r="K2" s="20">
-        <v>7</v>
-      </c>
-      <c r="L2" s="20">
-        <v>4</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="2" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
@@ -9742,7 +9019,7 @@
     <col min="12" max="12" width="23.453125" style="15" customWidth="1"/>
     <col min="13" max="13" width="18.81640625" style="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.81640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36" style="15" customWidth="1"/>
     <col min="16" max="16" width="12.26953125" style="15" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.81640625" style="15" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="25" style="15" bestFit="1" customWidth="1"/>
@@ -9814,7 +9091,7 @@
       <c r="N1" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="11" t="s">
         <v>51</v>
       </c>
       <c r="P1" s="15" t="s">
@@ -9896,131 +9173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="20">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="20">
-        <v>2</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="20">
-        <v>3</v>
-      </c>
-      <c r="L2" s="20">
-        <v>4</v>
-      </c>
-      <c r="M2" s="20">
-        <v>5</v>
-      </c>
-      <c r="N2" s="20">
-        <v>8</v>
-      </c>
-      <c r="O2" s="20">
-        <v>6</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="U2" s="20">
-        <v>7</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN2" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AO2" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="2" spans="1:41" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
@@ -10030,6 +9183,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
+      <c r="O3" s="11"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="38"/>
@@ -10350,26 +9504,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="17"/>
